--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR ZOTTI VINCENZO MARIA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR ZOTTI VINCENZO MARIA.xlsx
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -845,16 +845,16 @@
         <v>261</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>25</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>129</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>32</v>
@@ -913,7 +913,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>43</v>
@@ -922,14 +922,14 @@
         <v>47</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>50</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>11</v>
@@ -981,7 +981,7 @@
         <v>10</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>4</v>
@@ -1031,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>1</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
